--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.09909219971233</v>
+        <v>2.128602482453254</v>
       </c>
       <c r="D2" t="n">
-        <v>31.32202973650586</v>
+        <v>5.089829832182202</v>
       </c>
       <c r="E2" t="n">
-        <v>16.77248664421059</v>
+        <v>2.725529079684221</v>
       </c>
       <c r="F2" t="n">
-        <v>13.92941440675756</v>
+        <v>2.263529841098103</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.04454307609502</v>
+        <v>3.74473824986544</v>
       </c>
       <c r="D3" t="n">
-        <v>26.45488019139463</v>
+        <v>4.298918031101627</v>
       </c>
       <c r="E3" t="n">
-        <v>16.77248664421059</v>
+        <v>2.725529079684221</v>
       </c>
       <c r="F3" t="n">
-        <v>13.92941440675756</v>
+        <v>2.263529841098103</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.837281581832591</v>
+        <v>0.623558257047796</v>
       </c>
       <c r="D4" t="n">
-        <v>38.18272135077027</v>
+        <v>6.204692219500168</v>
       </c>
       <c r="E4" t="n">
-        <v>16.77248664421059</v>
+        <v>2.725529079684221</v>
       </c>
       <c r="F4" t="n">
-        <v>13.92941440675756</v>
+        <v>2.263529841098103</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.61773453539381</v>
+        <v>4.650381862001494</v>
       </c>
       <c r="D5" t="n">
-        <v>21.76478633105046</v>
+        <v>3.536777778795699</v>
       </c>
       <c r="E5" t="n">
-        <v>16.77248664421059</v>
+        <v>2.725529079684221</v>
       </c>
       <c r="F5" t="n">
-        <v>13.92941440675756</v>
+        <v>2.263529841098103</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.4218025410533</v>
+        <v>8.193542912921162</v>
       </c>
       <c r="D6" t="n">
-        <v>46.95210325427392</v>
+        <v>7.629716778819512</v>
       </c>
       <c r="E6" t="n">
-        <v>16.77248664421059</v>
+        <v>2.725529079684221</v>
       </c>
       <c r="F6" t="n">
-        <v>13.92941440675756</v>
+        <v>2.263529841098103</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.02490115310916</v>
+        <v>9.266546437380239</v>
       </c>
       <c r="D7" t="n">
-        <v>56.71780261715126</v>
+        <v>9.216642925287079</v>
       </c>
       <c r="E7" t="n">
-        <v>16.77248664421059</v>
+        <v>2.725529079684221</v>
       </c>
       <c r="F7" t="n">
-        <v>13.92941440675756</v>
+        <v>2.263529841098103</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.22575035478909</v>
+        <v>3.449184432653227</v>
       </c>
       <c r="D8" t="n">
-        <v>21.2494946345136</v>
+        <v>3.453042878108459</v>
       </c>
       <c r="E8" t="n">
-        <v>16.77248664421059</v>
+        <v>2.725529079684221</v>
       </c>
       <c r="F8" t="n">
-        <v>13.92941440675756</v>
+        <v>2.263529841098103</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.43687034883155</v>
+        <v>3.645991431685128</v>
       </c>
       <c r="D9" t="n">
-        <v>11.30085585643601</v>
+        <v>1.836389076670851</v>
       </c>
       <c r="E9" t="n">
-        <v>16.77248664421059</v>
+        <v>2.725529079684221</v>
       </c>
       <c r="F9" t="n">
-        <v>13.92941440675756</v>
+        <v>2.263529841098103</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
